--- a/Assets/10.Data/StructDataTable.xlsx
+++ b/Assets/10.Data/StructDataTable.xlsx
@@ -19,78 +19,81 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
+  <x:si>
+    <x:t>Count</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
   <x:si>
     <x:t>방향(칸)</x:t>
   </x:si>
   <x:si>
+    <x:t>Code</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item</x:t>
+  </x:si>
+  <x:si>
     <x:t>수치1</x:t>
   </x:si>
   <x:si>
     <x:t>한국어</x:t>
   </x:si>
   <x:si>
+    <x:t>수치2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수치3</x:t>
+  </x:si>
+  <x:si>
     <x:t>코드</x:t>
   </x:si>
   <x:si>
-    <x:t>수치2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수치3</x:t>
+    <x:t>STRUCT_PRODUCTION</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ITEM_NETWORKCHIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SpawnRange</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STR_STRUCT_ARMY_NAME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STR_STRUCT_TOWER_NAME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STR_STRUCT_DYNAMO_NAME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STRUCT_ARMY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SpecialItem</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이름(기획자용)</x:t>
   </x:si>
   <x:si>
     <x:t>ITEM_WIRE</x:t>
   </x:si>
   <x:si>
-    <x:t>SpecialItem</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STRUCT_ARMY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이름(기획자용)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STR_STRUCT_ARMY_NAME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STR_STRUCT_TOWER_NAME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STR_STRUCT_DYNAMO_NAME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Code</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Count</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ITEM_NETWORKCHIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STRUCT_PRODUCTION</x:t>
+    <x:t>Direction</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STR_STRUCT_PRODUCTION_NAME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ITEM_DISTURBE</x:t>
   </x:si>
   <x:si>
     <x:t>STRUCT_TOWER</x:t>
   </x:si>
   <x:si>
-    <x:t>ITEM_DISTURBE</x:t>
-  </x:si>
-  <x:si>
     <x:t>STRUCT_DYNAMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Direction</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STR_STRUCT_PRODUCTION_NAME</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -279,7 +282,10 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="14">
+  <x:cellXfs count="15">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -318,19 +324,6 @@
     <x:xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center" wrapText="1"/>
     </x:xf>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
     <x:xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center" wrapText="1"/>
     </x:xf>
@@ -372,6 +365,9 @@
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="표준" xfId="0" builtinId="0" iLevel="0"/>
@@ -1092,139 +1088,158 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:G45"/>
+  <x:dimension ref="A1:H45"/>
   <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.399999999999999"/>
   <x:cols>
-    <x:col min="2" max="2" width="29.5" style="1" customWidth="1"/>
-    <x:col min="3" max="3" width="29.125" style="1" customWidth="1"/>
-    <x:col min="4" max="4" width="29.125" customWidth="1"/>
-    <x:col min="6" max="6" width="9.00390625" style="2" bestFit="1" customWidth="1"/>
-    <x:col min="8" max="9" width="9.00390625" style="2" bestFit="1" customWidth="1"/>
+    <x:col min="2" max="2" width="29.5" style="2" customWidth="1"/>
+    <x:col min="3" max="3" width="29.125" style="2" customWidth="1"/>
+    <x:col min="4" max="4" width="10.77734375" style="1" customWidth="1"/>
+    <x:col min="5" max="5" width="10.77734375" customWidth="1"/>
+    <x:col min="6" max="6" width="20.77734375" customWidth="1"/>
+    <x:col min="7" max="7" width="10.77734375" style="3" customWidth="1"/>
+    <x:col min="8" max="8" width="20.77734375" customWidth="1"/>
+    <x:col min="9" max="10" width="9.00390625" style="3" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:7">
+    <x:row r="1" spans="1:8">
       <x:c r="A1" s="12" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B1" s="4" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="s">
+      <x:c r="C1" s="4" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D1" s="4" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E1" s="4"/>
+      <x:c r="F1" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G1" s="4" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H1" s="4" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:8">
+      <x:c r="A2" s="13"/>
+      <x:c r="B2" s="5" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C1" s="3" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D1" s="3" t="s">
+      <x:c r="C2" s="5" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D2" s="5" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E2" s="5" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F2" s="5" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G2" s="5" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E1" s="3" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F1" s="3" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G1" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:7" ht="28.75">
-      <x:c r="A2" s="13"/>
-      <x:c r="B2" s="4" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C2" s="4" t="s">
+      <x:c r="H2" s="5" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:8">
+      <x:c r="A3" s="6"/>
+      <x:c r="B3" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="s">
         <x:v>14</x:v>
-      </x:c>
-      <x:c r="D2" s="4" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E2" s="4" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F2" s="4" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G2" s="4" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:7" ht="28.75">
-      <x:c r="A3" s="5"/>
-      <x:c r="B3" s="6" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C3" s="7" t="s">
-        <x:v>11</x:v>
       </x:c>
       <x:c r="D3" s="7">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E3" s="8" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F3" s="8">
+      <x:c r="E3" s="7">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F3" s="8" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G3" s="8">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G3" s="8"/>
-    </x:row>
-    <x:row r="4" spans="1:7" ht="28.75">
-      <x:c r="A4" s="5"/>
-      <x:c r="B4" s="8" t="s">
-        <x:v>8</x:v>
+      <x:c r="H3" s="8"/>
+    </x:row>
+    <x:row r="4" spans="1:8">
+      <x:c r="A4" s="6"/>
+      <x:c r="B4" s="14" t="s">
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C4" s="7" t="s">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E4" s="8" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F4" s="8">
+      <x:c r="E4" s="7">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F4" s="8" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G4" s="8">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G4" s="8"/>
-    </x:row>
-    <x:row r="5" spans="1:7" ht="28.75">
-      <x:c r="A5" s="5"/>
-      <x:c r="B5" s="8" t="s">
-        <x:v>21</x:v>
+      <x:c r="H4" s="8"/>
+    </x:row>
+    <x:row r="5" spans="1:8">
+      <x:c r="A5" s="6"/>
+      <x:c r="B5" s="14" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C5" s="7" t="s">
-        <x:v>12</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D5" s="7">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E5" s="8" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F5" s="8">
+      <x:c r="E5" s="7">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F5" s="8" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G5" s="8">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G5" s="8"/>
-    </x:row>
-    <x:row r="6" spans="1:7" ht="42.899999999999999">
+      <x:c r="H5" s="8"/>
+    </x:row>
+    <x:row r="6" spans="1:8">
       <x:c r="A6" s="9"/>
-      <x:c r="B6" s="8" t="s">
-        <x:v>18</x:v>
+      <x:c r="B6" s="14" t="s">
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C6" s="8" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D6" s="8">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E6" s="8" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F6" s="8">
+      <x:c r="E6" s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F6" s="8" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G6" s="8">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G6" s="8" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:7">
+      <x:c r="H6" s="8" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:8">
       <x:c r="A7" s="9"/>
       <x:c r="B7" s="8"/>
       <x:c r="C7" s="8"/>
@@ -1232,8 +1247,9 @@
       <x:c r="E7" s="8"/>
       <x:c r="F7" s="8"/>
       <x:c r="G7" s="8"/>
-    </x:row>
-    <x:row r="8" spans="1:7">
+      <x:c r="H7" s="8"/>
+    </x:row>
+    <x:row r="8" spans="1:8">
       <x:c r="A8" s="9"/>
       <x:c r="B8" s="8"/>
       <x:c r="C8" s="8"/>
@@ -1241,8 +1257,9 @@
       <x:c r="E8" s="8"/>
       <x:c r="F8" s="8"/>
       <x:c r="G8" s="8"/>
-    </x:row>
-    <x:row r="9" spans="1:7">
+      <x:c r="H8" s="8"/>
+    </x:row>
+    <x:row r="9" spans="1:8">
       <x:c r="A9" s="9"/>
       <x:c r="B9" s="8"/>
       <x:c r="C9" s="8"/>
@@ -1250,8 +1267,9 @@
       <x:c r="E9" s="8"/>
       <x:c r="F9" s="8"/>
       <x:c r="G9" s="8"/>
-    </x:row>
-    <x:row r="10" spans="1:7">
+      <x:c r="H9" s="8"/>
+    </x:row>
+    <x:row r="10" spans="1:8">
       <x:c r="A10" s="9"/>
       <x:c r="B10" s="8"/>
       <x:c r="C10" s="8"/>
@@ -1259,8 +1277,9 @@
       <x:c r="E10" s="8"/>
       <x:c r="F10" s="8"/>
       <x:c r="G10" s="8"/>
-    </x:row>
-    <x:row r="11" spans="1:7">
+      <x:c r="H10" s="8"/>
+    </x:row>
+    <x:row r="11" spans="1:8">
       <x:c r="A11" s="9"/>
       <x:c r="B11" s="8"/>
       <x:c r="C11" s="8"/>
@@ -1268,8 +1287,9 @@
       <x:c r="E11" s="8"/>
       <x:c r="F11" s="8"/>
       <x:c r="G11" s="8"/>
-    </x:row>
-    <x:row r="12" spans="1:7">
+      <x:c r="H11" s="8"/>
+    </x:row>
+    <x:row r="12" spans="1:8">
       <x:c r="A12" s="9"/>
       <x:c r="B12" s="8"/>
       <x:c r="C12" s="8"/>
@@ -1277,8 +1297,9 @@
       <x:c r="E12" s="8"/>
       <x:c r="F12" s="8"/>
       <x:c r="G12" s="8"/>
-    </x:row>
-    <x:row r="13" spans="1:7">
+      <x:c r="H12" s="8"/>
+    </x:row>
+    <x:row r="13" spans="1:8">
       <x:c r="A13" s="9"/>
       <x:c r="B13" s="8"/>
       <x:c r="C13" s="8"/>
@@ -1286,8 +1307,9 @@
       <x:c r="E13" s="8"/>
       <x:c r="F13" s="8"/>
       <x:c r="G13" s="8"/>
-    </x:row>
-    <x:row r="14" spans="1:7">
+      <x:c r="H13" s="8"/>
+    </x:row>
+    <x:row r="14" spans="1:8">
       <x:c r="A14" s="9"/>
       <x:c r="B14" s="8"/>
       <x:c r="C14" s="8"/>
@@ -1295,8 +1317,9 @@
       <x:c r="E14" s="8"/>
       <x:c r="F14" s="8"/>
       <x:c r="G14" s="8"/>
-    </x:row>
-    <x:row r="15" spans="1:7">
+      <x:c r="H14" s="8"/>
+    </x:row>
+    <x:row r="15" spans="1:8">
       <x:c r="A15" s="9"/>
       <x:c r="B15" s="8"/>
       <x:c r="C15" s="8"/>
@@ -1304,8 +1327,9 @@
       <x:c r="E15" s="8"/>
       <x:c r="F15" s="8"/>
       <x:c r="G15" s="8"/>
-    </x:row>
-    <x:row r="16" spans="1:7">
+      <x:c r="H15" s="8"/>
+    </x:row>
+    <x:row r="16" spans="1:8">
       <x:c r="A16" s="9"/>
       <x:c r="B16" s="8"/>
       <x:c r="C16" s="8"/>
@@ -1313,8 +1337,9 @@
       <x:c r="E16" s="8"/>
       <x:c r="F16" s="8"/>
       <x:c r="G16" s="8"/>
-    </x:row>
-    <x:row r="17" spans="1:7">
+      <x:c r="H16" s="8"/>
+    </x:row>
+    <x:row r="17" spans="1:8">
       <x:c r="A17" s="9"/>
       <x:c r="B17" s="8"/>
       <x:c r="C17" s="8"/>
@@ -1322,8 +1347,9 @@
       <x:c r="E17" s="8"/>
       <x:c r="F17" s="8"/>
       <x:c r="G17" s="8"/>
-    </x:row>
-    <x:row r="18" spans="1:7">
+      <x:c r="H17" s="8"/>
+    </x:row>
+    <x:row r="18" spans="1:8">
       <x:c r="A18" s="9"/>
       <x:c r="B18" s="8"/>
       <x:c r="C18" s="8"/>
@@ -1331,8 +1357,9 @@
       <x:c r="E18" s="8"/>
       <x:c r="F18" s="8"/>
       <x:c r="G18" s="8"/>
-    </x:row>
-    <x:row r="19" spans="1:7">
+      <x:c r="H18" s="8"/>
+    </x:row>
+    <x:row r="19" spans="1:8">
       <x:c r="A19" s="9"/>
       <x:c r="B19" s="8"/>
       <x:c r="C19" s="8"/>
@@ -1340,8 +1367,9 @@
       <x:c r="E19" s="8"/>
       <x:c r="F19" s="8"/>
       <x:c r="G19" s="8"/>
-    </x:row>
-    <x:row r="20" spans="1:7">
+      <x:c r="H19" s="8"/>
+    </x:row>
+    <x:row r="20" spans="1:8">
       <x:c r="A20" s="9"/>
       <x:c r="B20" s="8"/>
       <x:c r="C20" s="8"/>
@@ -1349,8 +1377,9 @@
       <x:c r="E20" s="8"/>
       <x:c r="F20" s="8"/>
       <x:c r="G20" s="8"/>
-    </x:row>
-    <x:row r="21" spans="1:7">
+      <x:c r="H20" s="8"/>
+    </x:row>
+    <x:row r="21" spans="1:8">
       <x:c r="A21" s="9"/>
       <x:c r="B21" s="8"/>
       <x:c r="C21" s="8"/>
@@ -1358,8 +1387,9 @@
       <x:c r="E21" s="8"/>
       <x:c r="F21" s="8"/>
       <x:c r="G21" s="8"/>
-    </x:row>
-    <x:row r="22" spans="1:7">
+      <x:c r="H21" s="8"/>
+    </x:row>
+    <x:row r="22" spans="1:8">
       <x:c r="A22" s="9"/>
       <x:c r="B22" s="8"/>
       <x:c r="C22" s="8"/>
@@ -1367,8 +1397,9 @@
       <x:c r="E22" s="8"/>
       <x:c r="F22" s="8"/>
       <x:c r="G22" s="8"/>
-    </x:row>
-    <x:row r="23" spans="1:7">
+      <x:c r="H22" s="8"/>
+    </x:row>
+    <x:row r="23" spans="1:8">
       <x:c r="A23" s="9"/>
       <x:c r="B23" s="8"/>
       <x:c r="C23" s="8"/>
@@ -1376,8 +1407,9 @@
       <x:c r="E23" s="8"/>
       <x:c r="F23" s="8"/>
       <x:c r="G23" s="8"/>
-    </x:row>
-    <x:row r="24" spans="1:7">
+      <x:c r="H23" s="8"/>
+    </x:row>
+    <x:row r="24" spans="1:8">
       <x:c r="A24" s="9"/>
       <x:c r="B24" s="8"/>
       <x:c r="C24" s="8"/>
@@ -1385,8 +1417,9 @@
       <x:c r="E24" s="8"/>
       <x:c r="F24" s="8"/>
       <x:c r="G24" s="8"/>
-    </x:row>
-    <x:row r="25" spans="1:7">
+      <x:c r="H24" s="8"/>
+    </x:row>
+    <x:row r="25" spans="1:8">
       <x:c r="A25" s="9"/>
       <x:c r="B25" s="8"/>
       <x:c r="C25" s="8"/>
@@ -1394,8 +1427,9 @@
       <x:c r="E25" s="8"/>
       <x:c r="F25" s="8"/>
       <x:c r="G25" s="8"/>
-    </x:row>
-    <x:row r="26" spans="1:7">
+      <x:c r="H25" s="8"/>
+    </x:row>
+    <x:row r="26" spans="1:8">
       <x:c r="A26" s="9"/>
       <x:c r="B26" s="8"/>
       <x:c r="C26" s="8"/>
@@ -1403,8 +1437,9 @@
       <x:c r="E26" s="8"/>
       <x:c r="F26" s="8"/>
       <x:c r="G26" s="8"/>
-    </x:row>
-    <x:row r="27" spans="1:7">
+      <x:c r="H26" s="8"/>
+    </x:row>
+    <x:row r="27" spans="1:8">
       <x:c r="A27" s="9"/>
       <x:c r="B27" s="8"/>
       <x:c r="C27" s="8"/>
@@ -1412,8 +1447,9 @@
       <x:c r="E27" s="8"/>
       <x:c r="F27" s="8"/>
       <x:c r="G27" s="8"/>
-    </x:row>
-    <x:row r="28" spans="1:7">
+      <x:c r="H27" s="8"/>
+    </x:row>
+    <x:row r="28" spans="1:8">
       <x:c r="A28" s="9"/>
       <x:c r="B28" s="8"/>
       <x:c r="C28" s="8"/>
@@ -1421,8 +1457,9 @@
       <x:c r="E28" s="8"/>
       <x:c r="F28" s="8"/>
       <x:c r="G28" s="8"/>
-    </x:row>
-    <x:row r="29" spans="1:7">
+      <x:c r="H28" s="8"/>
+    </x:row>
+    <x:row r="29" spans="1:8">
       <x:c r="A29" s="9"/>
       <x:c r="B29" s="8"/>
       <x:c r="C29" s="8"/>
@@ -1430,8 +1467,9 @@
       <x:c r="E29" s="8"/>
       <x:c r="F29" s="8"/>
       <x:c r="G29" s="8"/>
-    </x:row>
-    <x:row r="30" spans="1:7">
+      <x:c r="H29" s="8"/>
+    </x:row>
+    <x:row r="30" spans="1:8">
       <x:c r="A30" s="9"/>
       <x:c r="B30" s="8"/>
       <x:c r="C30" s="8"/>
@@ -1439,8 +1477,9 @@
       <x:c r="E30" s="8"/>
       <x:c r="F30" s="8"/>
       <x:c r="G30" s="8"/>
-    </x:row>
-    <x:row r="31" spans="1:7">
+      <x:c r="H30" s="8"/>
+    </x:row>
+    <x:row r="31" spans="1:8">
       <x:c r="A31" s="9"/>
       <x:c r="B31" s="8"/>
       <x:c r="C31" s="8"/>
@@ -1448,8 +1487,9 @@
       <x:c r="E31" s="8"/>
       <x:c r="F31" s="8"/>
       <x:c r="G31" s="8"/>
-    </x:row>
-    <x:row r="32" spans="1:7">
+      <x:c r="H31" s="8"/>
+    </x:row>
+    <x:row r="32" spans="1:8">
       <x:c r="A32" s="9"/>
       <x:c r="B32" s="8"/>
       <x:c r="C32" s="8"/>
@@ -1457,8 +1497,9 @@
       <x:c r="E32" s="8"/>
       <x:c r="F32" s="8"/>
       <x:c r="G32" s="8"/>
-    </x:row>
-    <x:row r="33" spans="1:7">
+      <x:c r="H32" s="8"/>
+    </x:row>
+    <x:row r="33" spans="1:8">
       <x:c r="A33" s="9"/>
       <x:c r="B33" s="8"/>
       <x:c r="C33" s="8"/>
@@ -1466,8 +1507,9 @@
       <x:c r="E33" s="8"/>
       <x:c r="F33" s="8"/>
       <x:c r="G33" s="8"/>
-    </x:row>
-    <x:row r="34" spans="1:7">
+      <x:c r="H33" s="8"/>
+    </x:row>
+    <x:row r="34" spans="1:8">
       <x:c r="A34" s="9"/>
       <x:c r="B34" s="8"/>
       <x:c r="C34" s="8"/>
@@ -1475,8 +1517,9 @@
       <x:c r="E34" s="8"/>
       <x:c r="F34" s="8"/>
       <x:c r="G34" s="8"/>
-    </x:row>
-    <x:row r="35" spans="1:7">
+      <x:c r="H34" s="8"/>
+    </x:row>
+    <x:row r="35" spans="1:8">
       <x:c r="A35" s="9"/>
       <x:c r="B35" s="8"/>
       <x:c r="C35" s="8"/>
@@ -1484,8 +1527,9 @@
       <x:c r="E35" s="8"/>
       <x:c r="F35" s="8"/>
       <x:c r="G35" s="8"/>
-    </x:row>
-    <x:row r="36" spans="1:7">
+      <x:c r="H35" s="8"/>
+    </x:row>
+    <x:row r="36" spans="1:8">
       <x:c r="A36" s="9"/>
       <x:c r="B36" s="8"/>
       <x:c r="C36" s="8"/>
@@ -1493,8 +1537,9 @@
       <x:c r="E36" s="8"/>
       <x:c r="F36" s="8"/>
       <x:c r="G36" s="8"/>
-    </x:row>
-    <x:row r="37" spans="1:7">
+      <x:c r="H36" s="8"/>
+    </x:row>
+    <x:row r="37" spans="1:8">
       <x:c r="A37" s="9"/>
       <x:c r="B37" s="8"/>
       <x:c r="C37" s="8"/>
@@ -1502,8 +1547,9 @@
       <x:c r="E37" s="8"/>
       <x:c r="F37" s="8"/>
       <x:c r="G37" s="8"/>
-    </x:row>
-    <x:row r="38" spans="1:7">
+      <x:c r="H37" s="8"/>
+    </x:row>
+    <x:row r="38" spans="1:8">
       <x:c r="A38" s="9"/>
       <x:c r="B38" s="8"/>
       <x:c r="C38" s="8"/>
@@ -1511,8 +1557,9 @@
       <x:c r="E38" s="8"/>
       <x:c r="F38" s="8"/>
       <x:c r="G38" s="8"/>
-    </x:row>
-    <x:row r="39" spans="1:7">
+      <x:c r="H38" s="8"/>
+    </x:row>
+    <x:row r="39" spans="1:8">
       <x:c r="A39" s="9"/>
       <x:c r="B39" s="8"/>
       <x:c r="C39" s="8"/>
@@ -1520,8 +1567,9 @@
       <x:c r="E39" s="8"/>
       <x:c r="F39" s="8"/>
       <x:c r="G39" s="8"/>
-    </x:row>
-    <x:row r="40" spans="1:7">
+      <x:c r="H39" s="8"/>
+    </x:row>
+    <x:row r="40" spans="1:8">
       <x:c r="A40" s="9"/>
       <x:c r="B40" s="8"/>
       <x:c r="C40" s="8"/>
@@ -1529,8 +1577,9 @@
       <x:c r="E40" s="8"/>
       <x:c r="F40" s="8"/>
       <x:c r="G40" s="8"/>
-    </x:row>
-    <x:row r="41" spans="1:7">
+      <x:c r="H40" s="8"/>
+    </x:row>
+    <x:row r="41" spans="1:8">
       <x:c r="A41" s="9"/>
       <x:c r="B41" s="8"/>
       <x:c r="C41" s="8"/>
@@ -1538,8 +1587,9 @@
       <x:c r="E41" s="8"/>
       <x:c r="F41" s="8"/>
       <x:c r="G41" s="8"/>
-    </x:row>
-    <x:row r="42" spans="1:7">
+      <x:c r="H41" s="8"/>
+    </x:row>
+    <x:row r="42" spans="1:8">
       <x:c r="A42" s="9"/>
       <x:c r="B42" s="8"/>
       <x:c r="C42" s="8"/>
@@ -1547,8 +1597,9 @@
       <x:c r="E42" s="8"/>
       <x:c r="F42" s="8"/>
       <x:c r="G42" s="8"/>
-    </x:row>
-    <x:row r="43" spans="1:7">
+      <x:c r="H42" s="8"/>
+    </x:row>
+    <x:row r="43" spans="1:8">
       <x:c r="A43" s="9"/>
       <x:c r="B43" s="8"/>
       <x:c r="C43" s="8"/>
@@ -1556,8 +1607,9 @@
       <x:c r="E43" s="8"/>
       <x:c r="F43" s="8"/>
       <x:c r="G43" s="8"/>
-    </x:row>
-    <x:row r="44" spans="1:7">
+      <x:c r="H43" s="8"/>
+    </x:row>
+    <x:row r="44" spans="1:8">
       <x:c r="A44" s="9"/>
       <x:c r="B44" s="8"/>
       <x:c r="C44" s="8"/>
@@ -1565,8 +1617,9 @@
       <x:c r="E44" s="8"/>
       <x:c r="F44" s="8"/>
       <x:c r="G44" s="8"/>
-    </x:row>
-    <x:row r="45" spans="1:7">
+      <x:c r="H44" s="8"/>
+    </x:row>
+    <x:row r="45" spans="1:8">
       <x:c r="A45" s="10"/>
       <x:c r="B45" s="11"/>
       <x:c r="C45" s="11"/>
@@ -1574,6 +1627,7 @@
       <x:c r="E45" s="11"/>
       <x:c r="F45" s="11"/>
       <x:c r="G45" s="11"/>
+      <x:c r="H45" s="11"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells count="1">
